--- a/Results_Metaheuristic_improved.xlsx
+++ b/Results_Metaheuristic_improved.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/582755_student_fontys_nl/Documents/Leerjaar 2/Periode 1/Operations Research 5/OR5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_A7F68E5B70AFCAB4E36578BA4D65A6953D0222CA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DA731D3-26C2-4653-9EC7-3EA0F1DAE146}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_A7F68E5B4577C5DCEE0BB03B4BA9EED201BE22CB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5070A91D-0640-4933-B098-A2154A88ACE8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resultaten orders" sheetId="1" r:id="rId1"/>
@@ -48,100 +48,100 @@
     <t>ORD03</t>
   </si>
   <si>
+    <t>ORD01</t>
+  </si>
+  <si>
+    <t>ORD05</t>
+  </si>
+  <si>
+    <t>ORD02</t>
+  </si>
+  <si>
+    <t>ORD04</t>
+  </si>
+  <si>
     <t>ORD11</t>
   </si>
   <si>
-    <t>ORD01</t>
-  </si>
-  <si>
-    <t>ORD04</t>
+    <t>ORD09</t>
+  </si>
+  <si>
+    <t>ORD12</t>
+  </si>
+  <si>
+    <t>ORD06</t>
+  </si>
+  <si>
+    <t>ORD08</t>
   </si>
   <si>
     <t>ORD07</t>
   </si>
   <si>
-    <t>ORD02</t>
-  </si>
-  <si>
-    <t>ORD06</t>
+    <t>ORD10</t>
+  </si>
+  <si>
+    <t>ORD14</t>
   </si>
   <si>
     <t>ORD13</t>
   </si>
   <si>
-    <t>ORD09</t>
-  </si>
-  <si>
-    <t>ORD05</t>
+    <t>ORD20</t>
   </si>
   <si>
     <t>ORD25</t>
   </si>
   <si>
-    <t>ORD08</t>
+    <t>ORD15</t>
+  </si>
+  <si>
+    <t>ORD16</t>
+  </si>
+  <si>
+    <t>ORD26</t>
+  </si>
+  <si>
+    <t>ORD21</t>
+  </si>
+  <si>
+    <t>ORD19</t>
+  </si>
+  <si>
+    <t>ORD18</t>
+  </si>
+  <si>
+    <t>ORD17</t>
   </si>
   <si>
     <t>ORD27</t>
   </si>
   <si>
-    <t>ORD10</t>
-  </si>
-  <si>
-    <t>ORD12</t>
-  </si>
-  <si>
-    <t>ORD14</t>
-  </si>
-  <si>
-    <t>ORD16</t>
-  </si>
-  <si>
-    <t>ORD17</t>
-  </si>
-  <si>
-    <t>ORD15</t>
-  </si>
-  <si>
-    <t>ORD19</t>
-  </si>
-  <si>
-    <t>ORD20</t>
-  </si>
-  <si>
-    <t>ORD21</t>
-  </si>
-  <si>
     <t>ORD28</t>
   </si>
   <si>
-    <t>ORD26</t>
-  </si>
-  <si>
-    <t>ORD18</t>
-  </si>
-  <si>
     <t>ORD22</t>
   </si>
   <si>
+    <t>ORD23</t>
+  </si>
+  <si>
     <t>ORD24</t>
   </si>
   <si>
-    <t>ORD23</t>
-  </si>
-  <si>
     <t>Machine_number</t>
   </si>
   <si>
     <t>Order machine</t>
   </si>
   <si>
-    <t>ORD03 -&gt; ORD04 -&gt; ORD06 -&gt; ORD09 -&gt; ORD27 -&gt; ORD12 -&gt; ORD15 -&gt; ORD21 -&gt; ORD18 -&gt; ORD24</t>
-  </si>
-  <si>
-    <t>ORD11 -&gt; ORD02 -&gt; ORD05 -&gt; ORD08 -&gt; ORD14 -&gt; ORD17 -&gt; ORD20 -&gt; ORD26 -&gt; ORD22</t>
-  </si>
-  <si>
-    <t>ORD01 -&gt; ORD07 -&gt; ORD13 -&gt; ORD25 -&gt; ORD10 -&gt; ORD16 -&gt; ORD19 -&gt; ORD28 -&gt; ORD23</t>
+    <t>ORD03 -&gt; ORD04 -&gt; ORD09 -&gt; ORD06 -&gt; ORD07 -&gt; ORD13 -&gt; ORD25 -&gt; ORD16 -&gt; ORD19 -&gt; ORD27 -&gt; ORD28</t>
+  </si>
+  <si>
+    <t>ORD01 -&gt; ORD11 -&gt; ORD08 -&gt; ORD14 -&gt; ORD15 -&gt; ORD21 -&gt; ORD18 -&gt; ORD23</t>
+  </si>
+  <si>
+    <t>ORD05 -&gt; ORD02 -&gt; ORD12 -&gt; ORD10 -&gt; ORD20 -&gt; ORD26 -&gt; ORD17 -&gt; ORD22 -&gt; ORD24</t>
   </si>
   <si>
     <t>Resultaat</t>
@@ -494,9 +494,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -519,7 +522,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -542,7 +545,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -550,7 +553,7 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -562,10 +565,10 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -573,7 +576,7 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -585,10 +588,10 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>8.33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>7.22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -596,22 +599,22 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>7.5</v>
+        <v>7.22</v>
       </c>
       <c r="G5">
-        <v>14.58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18.329999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -619,45 +622,45 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>8.33</v>
+        <v>7.5</v>
       </c>
       <c r="G6">
-        <v>16.11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>14.58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="F7">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="G7">
-        <v>21.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -665,7 +668,7 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -677,33 +680,33 @@
         <v>14.58</v>
       </c>
       <c r="G8">
-        <v>21.25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>14</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>13.56</v>
       </c>
       <c r="C9">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>81.33</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9">
-        <v>16.11</v>
+        <v>19.329999999999998</v>
       </c>
       <c r="G9">
-        <v>22.22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <v>31.56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -711,7 +714,7 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -720,13 +723,13 @@
         <v>1</v>
       </c>
       <c r="F10">
-        <v>21.25</v>
+        <v>22.5</v>
       </c>
       <c r="G10">
         <v>29.17</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -734,7 +737,7 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -743,59 +746,59 @@
         <v>2</v>
       </c>
       <c r="F11">
-        <v>21.5</v>
+        <v>24</v>
       </c>
       <c r="G11">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>17</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C12">
         <v>14</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F12">
-        <v>22.22</v>
+        <v>33.17</v>
       </c>
       <c r="G12">
-        <v>33.89</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
       <c r="B13">
-        <v>0.5</v>
+        <v>0.22</v>
       </c>
       <c r="C13">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D13">
-        <v>6.5</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13">
-        <v>28</v>
+        <v>36.56</v>
       </c>
       <c r="G13">
-        <v>38.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+        <v>43.22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -803,22 +806,22 @@
         <v>0</v>
       </c>
       <c r="C14">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14">
-        <v>29.17</v>
+        <v>34.5</v>
       </c>
       <c r="G14">
-        <v>34.17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -826,68 +829,68 @@
         <v>0</v>
       </c>
       <c r="C15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F15">
-        <v>33.89</v>
+        <v>39</v>
       </c>
       <c r="G15">
-        <v>40.56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+        <v>43.58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>21</v>
       </c>
       <c r="B16">
-        <v>33.33</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D16">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16">
-        <v>42.17</v>
+        <v>48.22</v>
       </c>
       <c r="G16">
-        <v>51.33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56.56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>22</v>
       </c>
       <c r="B17">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C17">
         <v>14</v>
       </c>
       <c r="D17">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17">
-        <v>38.5</v>
+        <v>43.58</v>
       </c>
       <c r="G17">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+        <v>52.33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -895,22 +898,22 @@
         <v>0</v>
       </c>
       <c r="C18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18">
-        <v>43.56</v>
+        <v>48</v>
       </c>
       <c r="G18">
-        <v>52.44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -918,22 +921,22 @@
         <v>0</v>
       </c>
       <c r="C19">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19">
-        <v>51</v>
+        <v>55.33</v>
       </c>
       <c r="G19">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -941,22 +944,22 @@
         <v>0</v>
       </c>
       <c r="C20">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F20">
-        <v>51.33</v>
+        <v>56.56</v>
       </c>
       <c r="G20">
-        <v>61.33</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+        <v>68.78</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -964,22 +967,22 @@
         <v>0</v>
       </c>
       <c r="C21">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F21">
-        <v>52.44</v>
+        <v>60</v>
       </c>
       <c r="G21">
-        <v>63.56</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+        <v>68.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>27</v>
       </c>
@@ -987,45 +990,45 @@
         <v>0</v>
       </c>
       <c r="C22">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G22">
-        <v>65.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+        <v>70.33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>28</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C23">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23">
-        <v>61.33</v>
+        <v>68.5</v>
       </c>
       <c r="G23">
-        <v>68.42</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -1033,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="C24">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1042,13 +1045,13 @@
         <v>3</v>
       </c>
       <c r="F24">
-        <v>67.56</v>
+        <v>68.78</v>
       </c>
       <c r="G24">
-        <v>80.33</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+        <v>76.56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>30</v>
       </c>
@@ -1056,45 +1059,45 @@
         <v>0</v>
       </c>
       <c r="C25">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25">
-        <v>65.5</v>
+        <v>70.33</v>
       </c>
       <c r="G25">
-        <v>76.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+        <v>75.33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>31</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>6.92</v>
       </c>
       <c r="C26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>41.5</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26">
-        <v>68.42</v>
+        <v>79.33</v>
       </c>
       <c r="G26">
-        <v>77.17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+        <v>88.92</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -1108,16 +1111,16 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27">
-        <v>78.5</v>
+        <v>78.56</v>
       </c>
       <c r="G27">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+        <v>85.78</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -1125,22 +1128,22 @@
         <v>0</v>
       </c>
       <c r="C28">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D28">
         <v>0</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28">
-        <v>77.17</v>
+        <v>83</v>
       </c>
       <c r="G28">
-        <v>85.08</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>34</v>
       </c>
@@ -1148,7 +1151,7 @@
         <v>0</v>
       </c>
       <c r="C29">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -1157,10 +1160,10 @@
         <v>3</v>
       </c>
       <c r="F29">
-        <v>83.33</v>
+        <v>91.78</v>
       </c>
       <c r="G29">
-        <v>93.33</v>
+        <v>102.33</v>
       </c>
     </row>
   </sheetData>
@@ -1171,9 +1174,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>35</v>
       </c>
@@ -1181,7 +1184,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1189,7 +1192,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1197,7 +1200,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1213,12 +1216,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>40</v>
       </c>
@@ -1226,20 +1229,20 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>42</v>
       </c>
       <c r="B2">
-        <v>36.833300000000001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>29.694400000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>43</v>
       </c>
       <c r="B3">
-        <v>248.5</v>
+        <v>227.0556</v>
       </c>
     </row>
   </sheetData>

--- a/Results_Metaheuristic_improved.xlsx
+++ b/Results_Metaheuristic_improved.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ORD13</t>
+          <t>ORD02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -494,19 +494,19 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>4.58</v>
+        <v>8.33</v>
       </c>
       <c r="G2" t="n">
-        <v>4.58</v>
+        <v>8.33</v>
       </c>
       <c r="H2" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ORD02</t>
+          <t>ORD03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -533,19 +533,19 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H3" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -554,12 +554,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ORD26</t>
+          <t>ORD12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -572,19 +572,19 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>12.22</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
-        <v>12.22</v>
+        <v>11</v>
       </c>
       <c r="H4" t="n">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -593,37 +593,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ORD01</t>
+          <t>ORD04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>6.25</v>
+        <v>9.44</v>
       </c>
       <c r="G5" t="n">
-        <v>10.83</v>
+        <v>9.44</v>
       </c>
       <c r="H5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -637,7 +637,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -647,70 +647,70 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>10</v>
+        <v>8.33</v>
       </c>
       <c r="F6" t="n">
-        <v>11.5</v>
+        <v>9.58</v>
       </c>
       <c r="G6" t="n">
-        <v>21.5</v>
+        <v>17.92</v>
       </c>
       <c r="H6" t="n">
         <v>20</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>9</v>
       </c>
       <c r="K6" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ORD07</t>
+          <t>ORD01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>10.83</v>
+        <v>13</v>
       </c>
       <c r="F7" t="n">
-        <v>5.83</v>
+        <v>7.5</v>
       </c>
       <c r="G7" t="n">
-        <v>16.67</v>
+        <v>20.5</v>
       </c>
       <c r="H7" t="n">
+        <v>17</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>10</v>
+      </c>
+      <c r="K7" t="n">
         <v>35</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>14</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ORD08</t>
+          <t>ORD06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -725,22 +725,22 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>12.22</v>
+        <v>9.44</v>
       </c>
       <c r="F8" t="n">
-        <v>11.67</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>23.89</v>
+        <v>18.33</v>
       </c>
       <c r="H8" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -749,51 +749,51 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ORD04</t>
+          <t>ORD27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>19.67</v>
+        <v>15</v>
       </c>
       <c r="F9" t="n">
-        <v>7.08</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>26.75</v>
+        <v>21</v>
       </c>
       <c r="H9" t="n">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="I9" t="n">
-        <v>11.75</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ORD25</t>
+          <t>ORD08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -803,22 +803,22 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>23.5</v>
+        <v>17.92</v>
       </c>
       <c r="F10" t="n">
-        <v>10.5</v>
+        <v>8.75</v>
       </c>
       <c r="G10" t="n">
-        <v>34</v>
+        <v>26.67</v>
       </c>
       <c r="H10" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -827,7 +827,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ORD05</t>
+          <t>ORD14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -842,22 +842,22 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>23.89</v>
+        <v>28.33</v>
       </c>
       <c r="F11" t="n">
-        <v>7.22</v>
+        <v>13.89</v>
       </c>
       <c r="G11" t="n">
-        <v>31.11</v>
+        <v>42.22</v>
       </c>
       <c r="H11" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -866,76 +866,76 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ORD06</t>
+          <t>ORD07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>26.75</v>
+        <v>20.5</v>
       </c>
       <c r="F12" t="n">
-        <v>6.67</v>
+        <v>7</v>
       </c>
       <c r="G12" t="n">
-        <v>33.42</v>
+        <v>27.5</v>
       </c>
       <c r="H12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I12" t="n">
-        <v>2.4167</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K12" t="n">
-        <v>26.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORD14</t>
+          <t>ORD09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>31.11</v>
+        <v>21</v>
       </c>
       <c r="F13" t="n">
-        <v>13.89</v>
+        <v>9.5</v>
       </c>
       <c r="G13" t="n">
-        <v>45</v>
+        <v>30.5</v>
       </c>
       <c r="H13" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -944,7 +944,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ORD09</t>
+          <t>ORD05</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -953,37 +953,37 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>33.42</v>
+        <v>26.67</v>
       </c>
       <c r="F14" t="n">
-        <v>7.92</v>
+        <v>5.42</v>
       </c>
       <c r="G14" t="n">
-        <v>41.33</v>
+        <v>32.08</v>
       </c>
       <c r="H14" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I14" t="n">
-        <v>9.333299999999999</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K14" t="n">
-        <v>65.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ORD10</t>
+          <t>ORD25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -998,22 +998,22 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>34</v>
+        <v>27.5</v>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="G15" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H15" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1022,37 +1022,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ORD16</t>
+          <t>ORD10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>6</v>
+      </c>
+      <c r="G16" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="H16" t="n">
         <v>43</v>
       </c>
-      <c r="F16" t="n">
-        <v>8</v>
-      </c>
-      <c r="G16" t="n">
-        <v>51</v>
-      </c>
-      <c r="H16" t="n">
-        <v>63</v>
-      </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1070,19 +1070,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>49.33</v>
+        <v>33.08</v>
       </c>
       <c r="F17" t="n">
         <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>59.33</v>
+        <v>43.08</v>
       </c>
       <c r="H17" t="n">
         <v>66</v>
@@ -1100,12 +1100,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORD12</t>
+          <t>ORD19</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1115,64 +1115,64 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F18" t="n">
-        <v>12.22</v>
+        <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>58.22</v>
+        <v>51</v>
       </c>
       <c r="H18" t="n">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="I18" t="n">
-        <v>40.2222</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="K18" t="n">
-        <v>241.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ORD03</t>
+          <t>ORD13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>51</v>
+        <v>40.5</v>
       </c>
       <c r="F19" t="n">
-        <v>9</v>
+        <v>5.5</v>
       </c>
       <c r="G19" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="H19" t="n">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="I19" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K19" t="n">
-        <v>368</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1187,37 +1187,37 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>66.22</v>
+        <v>42.22</v>
       </c>
       <c r="F20" t="n">
         <v>8.33</v>
       </c>
       <c r="G20" t="n">
-        <v>74.56</v>
+        <v>50.56</v>
       </c>
       <c r="H20" t="n">
         <v>70</v>
       </c>
       <c r="I20" t="n">
-        <v>4.5556</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>12</v>
       </c>
       <c r="K20" t="n">
-        <v>54.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ORD21</t>
+          <t>ORD16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1226,28 +1226,28 @@
         </is>
       </c>
       <c r="C21" t="n">
+        <v>6</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>47.08</v>
+      </c>
+      <c r="F21" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="G21" t="n">
+        <v>53.75</v>
+      </c>
+      <c r="H21" t="n">
+        <v>63</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
         <v>8</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>59.33</v>
-      </c>
-      <c r="F21" t="n">
-        <v>7.08</v>
-      </c>
-      <c r="G21" t="n">
-        <v>66.42</v>
-      </c>
-      <c r="H21" t="n">
-        <v>69</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>7</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1256,37 +1256,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ORD19</t>
+          <t>ORD17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="C22" t="n">
+        <v>6</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>51</v>
+      </c>
+      <c r="F22" t="n">
         <v>7</v>
       </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>60</v>
-      </c>
-      <c r="F22" t="n">
-        <v>10</v>
-      </c>
       <c r="G22" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="H22" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1295,37 +1295,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ORD18</t>
+          <t>ORD21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>66.42</v>
+        <v>51.56</v>
       </c>
       <c r="F23" t="n">
-        <v>8.75</v>
+        <v>9.44</v>
       </c>
       <c r="G23" t="n">
-        <v>75.17</v>
+        <v>61</v>
       </c>
       <c r="H23" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ORD27</t>
+          <t>ORD18</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1343,19 +1343,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="G24" t="n">
-        <v>76</v>
+        <v>69.5</v>
       </c>
       <c r="H24" t="n">
         <v>78</v>
@@ -1364,7 +1364,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1373,12 +1373,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORD17</t>
+          <t>ORD26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1388,22 +1388,22 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>74.56</v>
+        <v>63.75</v>
       </c>
       <c r="F25" t="n">
-        <v>7.78</v>
+        <v>9.17</v>
       </c>
       <c r="G25" t="n">
-        <v>82.33</v>
+        <v>72.92</v>
       </c>
       <c r="H25" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1412,37 +1412,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ORD22</t>
+          <t>ORD23</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>80.17</v>
+        <v>69</v>
       </c>
       <c r="F26" t="n">
-        <v>5.42</v>
+        <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>85.58</v>
+        <v>78</v>
       </c>
       <c r="H26" t="n">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1456,71 +1456,71 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="F27" t="n">
-        <v>11.5</v>
+        <v>12.78</v>
       </c>
       <c r="G27" t="n">
-        <v>91.5</v>
+        <v>78.78</v>
       </c>
       <c r="H27" t="n">
         <v>82</v>
       </c>
       <c r="I27" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>6</v>
       </c>
       <c r="K27" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ORD23</t>
+          <t>ORD24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>93.33</v>
+        <v>69.5</v>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="G28" t="n">
-        <v>103.33</v>
+        <v>79</v>
       </c>
       <c r="H28" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1529,7 +1529,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ORD24</t>
+          <t>ORD22</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1538,28 +1538,28 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>91.58</v>
+        <v>74.92</v>
       </c>
       <c r="F29" t="n">
-        <v>7.92</v>
+        <v>5.42</v>
       </c>
       <c r="G29" t="n">
-        <v>99.5</v>
+        <v>80.33</v>
       </c>
       <c r="H29" t="n">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
